--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU340"/>
+  <dimension ref="A1:AU341"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G22">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G31">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G33">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G34">
@@ -6135,22 +6135,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G37">
@@ -6624,22 +6624,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G39">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G41">
@@ -7113,22 +7113,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G42">
@@ -7271,27 +7271,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G43">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-09-19 08:00:00</t>
+          <t>2026-09-19 08:15:00</t>
         </is>
       </c>
     </row>
@@ -7434,27 +7434,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G44">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-09-19 08:15:00</t>
+          <t>2026-09-19 08:30:00</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Pattani</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G45">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Pattani</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G47">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G50">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G51">
@@ -8743,22 +8743,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G54">
@@ -9232,22 +9232,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G56">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="G58">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="G59">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2026-09-19 08:30:00</t>
+          <t>2026-09-19 08:45:00</t>
         </is>
       </c>
     </row>
@@ -10042,12 +10042,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Sisaket United</t>
         </is>
       </c>
       <c r="G60">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-09-19 08:45:00</t>
+          <t>2026-09-19 09:00:00</t>
         </is>
       </c>
     </row>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sisaket United</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G61">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G62">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G63">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G64">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G68">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G69">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Adhyaksa</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Adhyaksa</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G71">
@@ -11998,12 +11998,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G72">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>2026-09-19 09:00:00</t>
+          <t>2026-09-19 09:30:00</t>
         </is>
       </c>
     </row>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G73">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G74">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G75">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>2026-09-19 09:30:00</t>
+          <t>2026-09-19 09:45:00</t>
         </is>
       </c>
     </row>
@@ -12655,7 +12655,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G83">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G84">
@@ -14117,12 +14117,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G85">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>2026-09-19 09:45:00</t>
+          <t>2026-09-19 10:00:00</t>
         </is>
       </c>
     </row>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G86">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G87">
@@ -14611,22 +14611,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G88">
@@ -14774,22 +14774,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G89">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G90">
@@ -15100,22 +15100,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G91">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G92">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G93">
@@ -15589,22 +15589,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G95">
@@ -15915,7 +15915,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G96">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G97">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G98">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G99">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G100">
@@ -16730,22 +16730,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G101">
@@ -17051,12 +17051,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G103">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>2026-09-19 10:00:00</t>
+          <t>2026-09-19 10:30:00</t>
         </is>
       </c>
     </row>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G106">
@@ -17708,7 +17708,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="G108">
@@ -18034,7 +18034,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G109">
@@ -18197,7 +18197,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G113">
@@ -18844,12 +18844,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G114">
@@ -18995,7 +18995,7 @@
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>2026-09-19 10:30:00</t>
+          <t>2026-09-19 11:00:00</t>
         </is>
       </c>
     </row>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G116">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G118">
@@ -19664,7 +19664,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,22 +20479,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G124">
@@ -20642,22 +20642,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G128">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G137">
@@ -22924,22 +22924,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G139">
@@ -23087,7 +23087,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G140">
@@ -23250,7 +23250,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G141">
@@ -23413,22 +23413,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G144">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G146">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G147">
@@ -24391,7 +24391,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G148">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G149">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G150">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G151">
@@ -25043,7 +25043,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G152">
@@ -25206,7 +25206,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G153">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G154">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G155">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G156">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G157">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G158">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G160">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G161">
@@ -26673,7 +26673,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G162">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G163">
@@ -26999,7 +26999,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G164">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G165">
@@ -27325,7 +27325,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G166">
@@ -27488,22 +27488,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G167">
@@ -27651,22 +27651,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G168">
@@ -27809,12 +27809,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G169">
@@ -27960,7 +27960,7 @@
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>2026-09-19 11:00:00</t>
+          <t>2026-09-19 11:15:00</t>
         </is>
       </c>
     </row>
@@ -27977,7 +27977,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G170">
@@ -28135,12 +28135,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="G171">
@@ -28286,7 +28286,7 @@
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>2026-09-19 11:15:00</t>
+          <t>2026-09-19 11:30:00</t>
         </is>
       </c>
     </row>
@@ -28303,7 +28303,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G172">
@@ -28629,7 +28629,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G174">
@@ -28792,22 +28792,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G175">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G176">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G177">
@@ -29281,22 +29281,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G178">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G179">
@@ -29607,7 +29607,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G180">
@@ -29649,13 +29649,13 @@
         </is>
       </c>
       <c r="N180">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O180">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P180">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="Q180">
         <v>0</v>
@@ -29770,7 +29770,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G181">
@@ -29812,13 +29812,13 @@
         </is>
       </c>
       <c r="N181">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O181">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P181">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="Q181">
         <v>0</v>
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Dinamo Zagreb II</t>
         </is>
       </c>
       <c r="G182">
@@ -30259,7 +30259,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G184">
@@ -30422,7 +30422,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G185">
@@ -30580,12 +30580,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G186">
@@ -30731,7 +30731,7 @@
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>2026-09-19 11:30:00</t>
+          <t>2026-09-19 12:00:00</t>
         </is>
       </c>
     </row>
@@ -30748,22 +30748,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G187">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="G193">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G194">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G203">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G204">
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G234">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G235">
@@ -43136,7 +43136,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G263">
@@ -43299,7 +43299,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G264">
@@ -43462,7 +43462,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G265">
@@ -43625,7 +43625,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G266">
@@ -43783,12 +43783,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G267">
@@ -43934,7 +43934,7 @@
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>2026-09-19 15:15:00</t>
+          <t>2026-09-19 15:00:00</t>
         </is>
       </c>
     </row>
@@ -43951,7 +43951,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G268">
@@ -44109,12 +44109,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G269">
@@ -44260,7 +44260,7 @@
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>2026-09-19 15:30:00</t>
+          <t>2026-09-19 15:15:00</t>
         </is>
       </c>
     </row>
@@ -44277,22 +44277,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G270">
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G271">
@@ -44929,22 +44929,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G274">
@@ -45092,7 +45092,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Atlético Paso</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Atletico Madrid III</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G275">
@@ -45255,7 +45255,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Atlético Paso</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Atletico Madrid III</t>
         </is>
       </c>
       <c r="G276">
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="G277">
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G278">
@@ -45744,7 +45744,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Valencia W</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G279">
@@ -45902,12 +45902,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Valencia W</t>
         </is>
       </c>
       <c r="G280">
@@ -46053,7 +46053,7 @@
       </c>
       <c r="AU280" t="inlineStr">
         <is>
-          <t>2026-09-19 15:45:00</t>
+          <t>2026-09-19 15:30:00</t>
         </is>
       </c>
     </row>
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G281">
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G282">
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G283">
@@ -46559,22 +46559,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G284">
@@ -46722,22 +46722,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G285">
@@ -46885,7 +46885,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G286">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G287">
@@ -47206,27 +47206,27 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G288">
@@ -47357,7 +47357,7 @@
       </c>
       <c r="AU288" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00:00</t>
+          <t>2026-09-19 15:45:00</t>
         </is>
       </c>
     </row>
@@ -47374,7 +47374,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G289">
@@ -47537,22 +47537,22 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G290">
@@ -47700,7 +47700,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G291">
@@ -47863,7 +47863,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G292">
@@ -48021,27 +48021,27 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G293">
@@ -48172,7 +48172,7 @@
       </c>
       <c r="AU293" t="inlineStr">
         <is>
-          <t>2026-09-19 16:30:00</t>
+          <t>2026-09-19 16:00:00</t>
         </is>
       </c>
     </row>
@@ -48189,22 +48189,22 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G294">
@@ -48352,22 +48352,22 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G295">
@@ -48510,12 +48510,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G296">
@@ -48661,7 +48661,7 @@
       </c>
       <c r="AU296" t="inlineStr">
         <is>
-          <t>2026-09-19 17:00:00</t>
+          <t>2026-09-19 16:30:00</t>
         </is>
       </c>
     </row>
@@ -48678,7 +48678,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G297">
@@ -48841,7 +48841,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G298">
@@ -48999,12 +48999,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G299">
@@ -49150,7 +49150,7 @@
       </c>
       <c r="AU299" t="inlineStr">
         <is>
-          <t>2026-09-19 18:00:00</t>
+          <t>2026-09-19 17:00:00</t>
         </is>
       </c>
     </row>
@@ -49167,7 +49167,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G300">
@@ -49325,12 +49325,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G301">
@@ -49476,7 +49476,7 @@
       </c>
       <c r="AU301" t="inlineStr">
         <is>
-          <t>2026-09-19 18:30:00</t>
+          <t>2026-09-19 18:00:00</t>
         </is>
       </c>
     </row>
@@ -49493,7 +49493,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G302">
@@ -49651,12 +49651,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G303">
@@ -49802,7 +49802,7 @@
       </c>
       <c r="AU303" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:00</t>
+          <t>2026-09-19 18:30:00</t>
         </is>
       </c>
     </row>
@@ -49814,12 +49814,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G304">
@@ -49965,7 +49965,7 @@
       </c>
       <c r="AU304" t="inlineStr">
         <is>
-          <t>2026-09-19 20:00:00</t>
+          <t>2026-09-19 19:30:00</t>
         </is>
       </c>
     </row>
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G305">
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G306">
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G307">
@@ -50629,12 +50629,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G309">
@@ -50780,7 +50780,7 @@
       </c>
       <c r="AU309" t="inlineStr">
         <is>
-          <t>2026-09-19 20:30:00</t>
+          <t>2026-09-19 20:00:00</t>
         </is>
       </c>
     </row>
@@ -50797,7 +50797,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -50807,12 +50807,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G310">
@@ -50970,12 +50970,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G311">
@@ -51123,7 +51123,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -51133,12 +51133,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G312">
@@ -51296,12 +51296,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G313">
@@ -51459,12 +51459,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G314">
@@ -51622,12 +51622,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G315">
@@ -51770,27 +51770,27 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G316">
@@ -51921,7 +51921,7 @@
       </c>
       <c r="AU316" t="inlineStr">
         <is>
-          <t>2026-09-19 21:00:00</t>
+          <t>2026-09-19 20:30:00</t>
         </is>
       </c>
     </row>
@@ -51948,12 +51948,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G317">
@@ -52101,22 +52101,22 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G318">
@@ -52264,7 +52264,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -52274,12 +52274,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G319">
@@ -52427,22 +52427,22 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G320">
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G321">
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G322">
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G323">
@@ -53089,12 +53089,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G324">
@@ -53252,12 +53252,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G325">
@@ -53415,12 +53415,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G326">
@@ -53578,12 +53578,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G327">
@@ -53726,27 +53726,27 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G328">
@@ -53877,7 +53877,7 @@
       </c>
       <c r="AU328" t="inlineStr">
         <is>
-          <t>2026-09-19 21:30:00</t>
+          <t>2026-09-19 21:00:00</t>
         </is>
       </c>
     </row>
@@ -53904,12 +53904,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G329">
@@ -54067,12 +54067,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G330">
@@ -54230,12 +54230,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G331">
@@ -54393,12 +54393,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G332">
@@ -54541,12 +54541,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -54556,12 +54556,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G333">
@@ -54692,7 +54692,7 @@
       </c>
       <c r="AU333" t="inlineStr">
         <is>
-          <t>2026-09-19 21:45:00</t>
+          <t>2026-09-19 21:30:00</t>
         </is>
       </c>
     </row>
@@ -54704,12 +54704,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -54719,12 +54719,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G334">
@@ -54855,7 +54855,7 @@
       </c>
       <c r="AU334" t="inlineStr">
         <is>
-          <t>2026-09-19 22:00:00</t>
+          <t>2026-09-19 21:45:00</t>
         </is>
       </c>
     </row>
@@ -54867,12 +54867,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -54882,12 +54882,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G335">
@@ -55018,7 +55018,7 @@
       </c>
       <c r="AU335" t="inlineStr">
         <is>
-          <t>2026-09-19 22:30:00</t>
+          <t>2026-09-19 22:00:00</t>
         </is>
       </c>
     </row>
@@ -55045,12 +55045,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G336">
@@ -55356,12 +55356,12 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G338">
@@ -55507,7 +55507,7 @@
       </c>
       <c r="AU338" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00:00</t>
+          <t>2026-09-19 22:30:00</t>
         </is>
       </c>
     </row>
@@ -55519,7 +55519,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G339">
@@ -55670,7 +55670,7 @@
       </c>
       <c r="AU339" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30:00</t>
+          <t>2026-09-19 23:00:00</t>
         </is>
       </c>
     </row>
@@ -55687,151 +55687,314 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Las Vegas Lights</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Hartford Athletic</t>
+        </is>
+      </c>
+      <c r="G340">
+        <v>0</v>
+      </c>
+      <c r="H340">
+        <v>0</v>
+      </c>
+      <c r="I340">
+        <v>0</v>
+      </c>
+      <c r="J340">
+        <v>0</v>
+      </c>
+      <c r="K340">
+        <v>0</v>
+      </c>
+      <c r="L340">
+        <v>0</v>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N340">
+        <v>0</v>
+      </c>
+      <c r="O340">
+        <v>0</v>
+      </c>
+      <c r="P340">
+        <v>0</v>
+      </c>
+      <c r="Q340">
+        <v>0</v>
+      </c>
+      <c r="R340">
+        <v>0</v>
+      </c>
+      <c r="S340">
+        <v>0</v>
+      </c>
+      <c r="T340">
+        <v>0</v>
+      </c>
+      <c r="U340">
+        <v>0</v>
+      </c>
+      <c r="V340">
+        <v>0</v>
+      </c>
+      <c r="W340">
+        <v>0</v>
+      </c>
+      <c r="X340">
+        <v>0</v>
+      </c>
+      <c r="Y340">
+        <v>0</v>
+      </c>
+      <c r="Z340">
+        <v>0</v>
+      </c>
+      <c r="AA340">
+        <v>0</v>
+      </c>
+      <c r="AB340">
+        <v>0</v>
+      </c>
+      <c r="AC340">
+        <v>0</v>
+      </c>
+      <c r="AD340">
+        <v>0</v>
+      </c>
+      <c r="AE340">
+        <v>0</v>
+      </c>
+      <c r="AF340">
+        <v>0</v>
+      </c>
+      <c r="AG340">
+        <v>0</v>
+      </c>
+      <c r="AH340" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI340" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ340">
+        <v>0</v>
+      </c>
+      <c r="AK340">
+        <v>0</v>
+      </c>
+      <c r="AL340">
+        <v>0</v>
+      </c>
+      <c r="AM340">
+        <v>-1</v>
+      </c>
+      <c r="AN340">
+        <v>-1</v>
+      </c>
+      <c r="AO340">
+        <v>-1</v>
+      </c>
+      <c r="AP340">
+        <v>-1</v>
+      </c>
+      <c r="AQ340">
+        <v>0</v>
+      </c>
+      <c r="AR340">
+        <v>0</v>
+      </c>
+      <c r="AS340">
+        <v>0</v>
+      </c>
+      <c r="AT340">
+        <v>0</v>
+      </c>
+      <c r="AU340" t="inlineStr">
+        <is>
+          <t>2026-09-19 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr">
+      <c r="D341" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E340" t="inlineStr">
+      <c r="E341" t="inlineStr">
         <is>
           <t>Portland Timbers</t>
         </is>
       </c>
-      <c r="F340" t="inlineStr">
+      <c r="F341" t="inlineStr">
         <is>
           <t>Atlanta United FC</t>
         </is>
       </c>
-      <c r="G340">
-        <v>0</v>
-      </c>
-      <c r="H340">
-        <v>0</v>
-      </c>
-      <c r="I340">
-        <v>0</v>
-      </c>
-      <c r="J340">
-        <v>0</v>
-      </c>
-      <c r="K340">
-        <v>0</v>
-      </c>
-      <c r="L340">
-        <v>0</v>
-      </c>
-      <c r="M340" t="inlineStr">
+      <c r="G341">
+        <v>0</v>
+      </c>
+      <c r="H341">
+        <v>0</v>
+      </c>
+      <c r="I341">
+        <v>0</v>
+      </c>
+      <c r="J341">
+        <v>0</v>
+      </c>
+      <c r="K341">
+        <v>0</v>
+      </c>
+      <c r="L341">
+        <v>0</v>
+      </c>
+      <c r="M341" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N340">
-        <v>0</v>
-      </c>
-      <c r="O340">
-        <v>0</v>
-      </c>
-      <c r="P340">
-        <v>0</v>
-      </c>
-      <c r="Q340">
-        <v>0</v>
-      </c>
-      <c r="R340">
-        <v>0</v>
-      </c>
-      <c r="S340">
-        <v>0</v>
-      </c>
-      <c r="T340">
-        <v>0</v>
-      </c>
-      <c r="U340">
-        <v>0</v>
-      </c>
-      <c r="V340">
-        <v>0</v>
-      </c>
-      <c r="W340">
-        <v>0</v>
-      </c>
-      <c r="X340">
-        <v>0</v>
-      </c>
-      <c r="Y340">
-        <v>0</v>
-      </c>
-      <c r="Z340">
-        <v>0</v>
-      </c>
-      <c r="AA340">
-        <v>0</v>
-      </c>
-      <c r="AB340">
-        <v>0</v>
-      </c>
-      <c r="AC340">
-        <v>0</v>
-      </c>
-      <c r="AD340">
-        <v>0</v>
-      </c>
-      <c r="AE340">
-        <v>0</v>
-      </c>
-      <c r="AF340">
-        <v>0</v>
-      </c>
-      <c r="AG340">
-        <v>0</v>
-      </c>
-      <c r="AH340" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI340" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ340">
-        <v>0</v>
-      </c>
-      <c r="AK340">
-        <v>0</v>
-      </c>
-      <c r="AL340">
-        <v>0</v>
-      </c>
-      <c r="AM340">
-        <v>-1</v>
-      </c>
-      <c r="AN340">
-        <v>-1</v>
-      </c>
-      <c r="AO340">
-        <v>-1</v>
-      </c>
-      <c r="AP340">
-        <v>-1</v>
-      </c>
-      <c r="AQ340">
-        <v>0</v>
-      </c>
-      <c r="AR340">
-        <v>0</v>
-      </c>
-      <c r="AS340">
-        <v>0</v>
-      </c>
-      <c r="AT340">
-        <v>0</v>
-      </c>
-      <c r="AU340" t="inlineStr">
+      <c r="N341">
+        <v>0</v>
+      </c>
+      <c r="O341">
+        <v>0</v>
+      </c>
+      <c r="P341">
+        <v>0</v>
+      </c>
+      <c r="Q341">
+        <v>0</v>
+      </c>
+      <c r="R341">
+        <v>0</v>
+      </c>
+      <c r="S341">
+        <v>0</v>
+      </c>
+      <c r="T341">
+        <v>0</v>
+      </c>
+      <c r="U341">
+        <v>0</v>
+      </c>
+      <c r="V341">
+        <v>0</v>
+      </c>
+      <c r="W341">
+        <v>0</v>
+      </c>
+      <c r="X341">
+        <v>0</v>
+      </c>
+      <c r="Y341">
+        <v>0</v>
+      </c>
+      <c r="Z341">
+        <v>0</v>
+      </c>
+      <c r="AA341">
+        <v>0</v>
+      </c>
+      <c r="AB341">
+        <v>0</v>
+      </c>
+      <c r="AC341">
+        <v>0</v>
+      </c>
+      <c r="AD341">
+        <v>0</v>
+      </c>
+      <c r="AE341">
+        <v>0</v>
+      </c>
+      <c r="AF341">
+        <v>0</v>
+      </c>
+      <c r="AG341">
+        <v>0</v>
+      </c>
+      <c r="AH341" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI341" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ341">
+        <v>0</v>
+      </c>
+      <c r="AK341">
+        <v>0</v>
+      </c>
+      <c r="AL341">
+        <v>0</v>
+      </c>
+      <c r="AM341">
+        <v>-1</v>
+      </c>
+      <c r="AN341">
+        <v>-1</v>
+      </c>
+      <c r="AO341">
+        <v>-1</v>
+      </c>
+      <c r="AP341">
+        <v>-1</v>
+      </c>
+      <c r="AQ341">
+        <v>0</v>
+      </c>
+      <c r="AR341">
+        <v>0</v>
+      </c>
+      <c r="AS341">
+        <v>0</v>
+      </c>
+      <c r="AT341">
+        <v>0</v>
+      </c>
+      <c r="AU341" t="inlineStr">
         <is>
           <t>2026-09-19 23:30:00</t>
         </is>

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G24">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Adhyaksa</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Adhyaksa</t>
         </is>
       </c>
       <c r="G71">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G73">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G74">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G83">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G86">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G87">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G91">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G92">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G93">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G96">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G97">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G123">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G145">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G146">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G147">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G207">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G208">
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G234">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G235">
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G271">
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G272">
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G273">
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G274">
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G307">
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G308">
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G309">
@@ -51622,12 +51622,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G315">
@@ -51785,12 +51785,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G316">
@@ -51948,12 +51948,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G317">
@@ -52111,12 +52111,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G318">
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G323">
@@ -53089,12 +53089,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G324">
@@ -53252,12 +53252,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G325">
@@ -53415,12 +53415,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G326">
@@ -53578,12 +53578,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G327">
@@ -53741,12 +53741,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G328">

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Adhyaksa</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Adhyaksa</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G71">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G92">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G93">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G123">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G145">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G146">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G147">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G149">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G150">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G151">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G153">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G154">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G155">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G156">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G157">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G158">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G159">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G160">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G161">
@@ -51622,12 +51622,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G315">
@@ -51785,12 +51785,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G316">
@@ -53252,12 +53252,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G325">
@@ -53415,12 +53415,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G326">
@@ -53578,12 +53578,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G327">
@@ -53741,12 +53741,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G328">
